--- a/data/trans_dic/P19C03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 43,06</t>
+          <t>29,01; 42,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,99; 23,94</t>
+          <t>14,45; 24,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,79; 33,82</t>
+          <t>22,31; 34,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 19,38</t>
+          <t>10,38; 19,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,46; 48,43</t>
+          <t>33,83; 49,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,79; 32,69</t>
+          <t>20,33; 32,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 27,58</t>
+          <t>17,19; 27,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 27,96</t>
+          <t>18,7; 27,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,24; 43,58</t>
+          <t>33,33; 43,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 26,39</t>
+          <t>18,59; 26,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,14; 28,66</t>
+          <t>21,12; 29,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,34; 22,5</t>
+          <t>15,33; 22,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,46; 38,57</t>
+          <t>29,27; 38,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,82; 34,97</t>
+          <t>26,06; 35,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 38,01</t>
+          <t>26,82; 37,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,55; 32,55</t>
+          <t>22,47; 33,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 35,2</t>
+          <t>26,84; 35,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,45; 35,76</t>
+          <t>26,32; 35,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,22; 31,24</t>
+          <t>22,31; 31,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,87; 25,79</t>
+          <t>18,49; 25,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,08; 35,35</t>
+          <t>29,27; 35,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,22; 34,05</t>
+          <t>27,61; 34,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,46; 33,06</t>
+          <t>26,37; 33,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,78; 28,0</t>
+          <t>21,43; 27,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,89; 38,03</t>
+          <t>25,81; 38,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,76; 38,35</t>
+          <t>27,56; 38,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,76; 32,62</t>
+          <t>22,51; 32,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 22,81</t>
+          <t>13,67; 22,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,73; 34,94</t>
+          <t>25,2; 35,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,84; 31,9</t>
+          <t>21,98; 31,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,45; 28,92</t>
+          <t>19,32; 29,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 17,02</t>
+          <t>11,43; 17,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,64; 34,75</t>
+          <t>26,57; 34,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,76; 33,42</t>
+          <t>26,23; 33,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,63; 29,88</t>
+          <t>22,61; 29,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 18,85</t>
+          <t>13,48; 18,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,07; 37,59</t>
+          <t>25,92; 37,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 38,91</t>
+          <t>28,56; 39,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 23,01</t>
+          <t>14,23; 22,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 27,01</t>
+          <t>13,68; 26,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,12; 37,16</t>
+          <t>27,09; 37,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,57; 29,84</t>
+          <t>20,05; 29,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 29,15</t>
+          <t>19,79; 30,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,29; 40,09</t>
+          <t>12,41; 37,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,84; 35,43</t>
+          <t>27,81; 35,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,45; 33,19</t>
+          <t>25,64; 32,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 24,48</t>
+          <t>18,21; 24,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 30,62</t>
+          <t>15,0; 31,61</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 35,78</t>
+          <t>21,89; 35,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,15; 38,96</t>
+          <t>24,64; 38,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,59; 31,99</t>
+          <t>16,7; 32,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,62; 27,03</t>
+          <t>16,73; 27,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 35,52</t>
+          <t>20,99; 35,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,44; 37,08</t>
+          <t>23,51; 36,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,74; 31,55</t>
+          <t>18,03; 31,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,04; 27,25</t>
+          <t>18,95; 26,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,6; 33,08</t>
+          <t>23,64; 33,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,21; 35,66</t>
+          <t>25,98; 35,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,34; 29,61</t>
+          <t>18,69; 29,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 25,3</t>
+          <t>19,16; 25,32</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,34; 35,64</t>
+          <t>23,03; 35,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,42; 32,8</t>
+          <t>20,41; 32,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,47; 28,23</t>
+          <t>17,19; 28,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,38; 29,0</t>
+          <t>18,56; 28,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,19; 32,66</t>
+          <t>20,61; 32,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,56; 32,19</t>
+          <t>21,59; 32,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,31; 26,65</t>
+          <t>16,95; 26,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 20,08</t>
+          <t>12,54; 20,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,23; 32,33</t>
+          <t>23,06; 31,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,55; 30,31</t>
+          <t>22,89; 30,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,3; 25,72</t>
+          <t>18,27; 25,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,54; 23,24</t>
+          <t>16,8; 23,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,77; 37,71</t>
+          <t>28,9; 38,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,16; 34,48</t>
+          <t>26,22; 34,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,09; 40,38</t>
+          <t>31,01; 40,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,49; 27,33</t>
+          <t>19,26; 27,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,45; 35,42</t>
+          <t>26,83; 35,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,88; 31,57</t>
+          <t>23,82; 31,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,62; 37,32</t>
+          <t>28,78; 37,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 21,83</t>
+          <t>7,15; 21,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,2; 35,36</t>
+          <t>29,24; 34,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,91; 31,45</t>
+          <t>26,23; 31,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,28; 37,78</t>
+          <t>31,16; 37,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,24; 22,68</t>
+          <t>11,62; 22,79</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,99; 34,73</t>
+          <t>26,78; 34,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,18; 35,9</t>
+          <t>28,26; 35,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 29,68</t>
+          <t>23,01; 30,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,47</t>
+          <t>3,43; 11,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,95; 39,26</t>
+          <t>31,01; 39,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,14; 37,61</t>
+          <t>30,22; 37,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,01; 30,67</t>
+          <t>23,93; 30,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,34; 14,36</t>
+          <t>10,26; 14,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,23; 35,87</t>
+          <t>30,29; 35,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,19; 35,38</t>
+          <t>30,11; 35,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,21; 29,04</t>
+          <t>24,32; 29,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 11,9</t>
+          <t>6,01; 11,82</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30,08; 34,04</t>
+          <t>30,09; 33,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,16; 31,77</t>
+          <t>28,27; 31,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25,65; 29,28</t>
+          <t>25,99; 29,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,9; 20,19</t>
+          <t>13,8; 20,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,12; 33,87</t>
+          <t>30,36; 33,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,05; 30,57</t>
+          <t>27,43; 30,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,66; 27,87</t>
+          <t>24,69; 28,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,48; 19,96</t>
+          <t>14,53; 19,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,28</t>
+          <t>30,82; 33,32</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28,31; 30,8</t>
+          <t>28,31; 30,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25,65; 28,05</t>
+          <t>25,61; 28,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,26; 19,35</t>
+          <t>15,51; 19,38</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55581; 82459</t>
+          <t>55554; 81751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35052; 59992</t>
+          <t>36195; 60288</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53444; 82922</t>
+          <t>54706; 84334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32667; 59181</t>
+          <t>31714; 60131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>69338; 97462</t>
+          <t>68072; 98704</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51825; 81476</t>
+          <t>50662; 80638</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42779; 67929</t>
+          <t>42349; 68352</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53135; 80426</t>
+          <t>53776; 79821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>130530; 171142</t>
+          <t>130891; 170114</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92787; 131879</t>
+          <t>92927; 133330</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103915; 140891</t>
+          <t>103819; 142971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90959; 133446</t>
+          <t>90920; 132590</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120407; 157647</t>
+          <t>119622; 158252</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>104910; 142082</t>
+          <t>105875; 143740</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102599; 138027</t>
+          <t>97406; 136071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>114334; 165010</t>
+          <t>113903; 170626</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>117935; 155292</t>
+          <t>118420; 155637</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>115539; 156195</t>
+          <t>114994; 154533</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87395; 122874</t>
+          <t>87766; 122548</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94653; 129324</t>
+          <t>92759; 129753</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247120; 300425</t>
+          <t>248806; 301791</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>229478; 287102</t>
+          <t>232809; 287378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200163; 250128</t>
+          <t>199472; 249932</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>219613; 282419</t>
+          <t>216151; 280441</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61233; 89956</t>
+          <t>61048; 90528</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81520; 112622</t>
+          <t>80930; 111783</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66110; 94766</t>
+          <t>65398; 95764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41782; 68706</t>
+          <t>41162; 68359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71425; 100919</t>
+          <t>72772; 102760</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71816; 104873</t>
+          <t>72275; 103740</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59855; 89017</t>
+          <t>59465; 89247</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35882; 57076</t>
+          <t>38335; 59751</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139962; 182535</t>
+          <t>139574; 181191</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>160338; 207990</t>
+          <t>163259; 208357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135392; 178744</t>
+          <t>135254; 176332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84676; 119993</t>
+          <t>85812; 120365</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69756; 100558</t>
+          <t>69355; 99574</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88247; 121827</t>
+          <t>89428; 124350</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46423; 75944</t>
+          <t>46973; 74295</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42622; 83762</t>
+          <t>42432; 81789</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>81236; 111316</t>
+          <t>81142; 113422</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70528; 102302</t>
+          <t>68726; 102337</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68970; 101707</t>
+          <t>69053; 104922</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62937; 189822</t>
+          <t>58776; 179504</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>157881; 200919</t>
+          <t>157700; 201655</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166899; 217706</t>
+          <t>168171; 215794</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124175; 166193</t>
+          <t>123636; 166116</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114872; 239908</t>
+          <t>117555; 247720</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37068; 60922</t>
+          <t>37268; 60655</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48303; 74835</t>
+          <t>47319; 74513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19783; 38141</t>
+          <t>19910; 38426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27996; 45534</t>
+          <t>28176; 45685</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37852; 61772</t>
+          <t>36495; 62007</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45610; 72156</t>
+          <t>45745; 71817</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25816; 45912</t>
+          <t>26230; 45679</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38515; 55119</t>
+          <t>38334; 53750</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81231; 113862</t>
+          <t>81380; 115050</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>101348; 137858</t>
+          <t>100440; 138092</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51193; 78375</t>
+          <t>49466; 77175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69431; 93788</t>
+          <t>71014; 93870</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42292; 67462</t>
+          <t>43580; 67433</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51032; 81983</t>
+          <t>51029; 80633</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40812; 65953</t>
+          <t>40169; 66223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46635; 73594</t>
+          <t>47102; 71132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41278; 66791</t>
+          <t>42153; 66403</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57104; 85244</t>
+          <t>57177; 85881</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40312; 65863</t>
+          <t>41902; 66569</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31161; 49473</t>
+          <t>30883; 49913</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91481; 127297</t>
+          <t>90788; 124358</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>116072; 156031</t>
+          <t>117848; 157843</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87959; 123648</t>
+          <t>87820; 124717</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>82733; 116195</t>
+          <t>84036; 115025</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>133590; 175119</t>
+          <t>134196; 176500</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>149704; 197334</t>
+          <t>150075; 196057</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>137512; 178589</t>
+          <t>137167; 179736</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116878; 163875</t>
+          <t>115528; 164467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>148075; 191061</t>
+          <t>144729; 189091</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>149291; 197330</t>
+          <t>148913; 197500</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>139384; 181759</t>
+          <t>140158; 181739</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>59076; 180699</t>
+          <t>59144; 179755</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>293071; 354927</t>
+          <t>293446; 351038</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>310218; 376587</t>
+          <t>314096; 378964</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>290729; 351157</t>
+          <t>289606; 348521</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>160474; 323767</t>
+          <t>165850; 325307</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>141828; 182541</t>
+          <t>140750; 183317</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>178664; 227558</t>
+          <t>179170; 227334</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>146522; 190050</t>
+          <t>147318; 192066</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29310; 104101</t>
+          <t>31160; 102636</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>183352; 232556</t>
+          <t>183690; 231938</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>211659; 264104</t>
+          <t>212248; 261683</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>166017; 212024</t>
+          <t>165414; 212512</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>72816; 101109</t>
+          <t>72228; 99472</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>337979; 401030</t>
+          <t>338636; 402208</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>403445; 472697</t>
+          <t>402365; 473401</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>322365; 386742</t>
+          <t>323788; 388244</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>91155; 191804</t>
+          <t>96851; 190484</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>738000; 835283</t>
+          <t>738252; 831122</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>819942; 925148</t>
+          <t>823239; 931331</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>683521; 780111</t>
+          <t>692520; 783155</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>466080; 677159</t>
+          <t>462873; 672309</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>825485; 928483</t>
+          <t>832173; 926843</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>850603; 961140</t>
+          <t>862414; 965794</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>707216; 799085</t>
+          <t>707993; 804134</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>518144; 714249</t>
+          <t>520003; 711757</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1595910; 1728616</t>
+          <t>1600758; 1731109</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1714774; 1865452</t>
+          <t>1714290; 1857413</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1419039; 1551376</t>
+          <t>1416417; 1558872</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1057834; 1341274</t>
+          <t>1075093; 1342961</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,01; 42,69</t>
+          <t>29,02; 42,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 24,06</t>
+          <t>14,26; 24,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,31; 34,39</t>
+          <t>21,86; 34,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 19,69</t>
+          <t>12,99; 21,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,83; 49,05</t>
+          <t>33,45; 47,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,33; 32,35</t>
+          <t>20,56; 32,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 27,75</t>
+          <t>17,19; 27,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,7; 27,75</t>
+          <t>19,92; 28,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,33; 43,32</t>
+          <t>33,67; 43,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,59; 26,68</t>
+          <t>18,84; 26,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,12; 29,09</t>
+          <t>21,0; 29,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,36</t>
+          <t>17,62; 24,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,27; 38,72</t>
+          <t>28,81; 38,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 35,38</t>
+          <t>26,04; 35,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,82; 37,47</t>
+          <t>27,42; 37,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,47; 33,66</t>
+          <t>22,45; 32,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,84; 35,28</t>
+          <t>26,12; 35,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,32; 35,38</t>
+          <t>26,73; 35,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,31; 31,16</t>
+          <t>22,04; 31,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 25,87</t>
+          <t>19,07; 25,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,27; 35,51</t>
+          <t>29,22; 35,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,61; 34,08</t>
+          <t>27,4; 33,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,04</t>
+          <t>26,2; 33,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,43; 27,81</t>
+          <t>21,62; 27,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,81; 38,27</t>
+          <t>25,54; 37,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,56; 38,06</t>
+          <t>27,4; 38,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,51; 32,96</t>
+          <t>23,05; 33,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,67; 22,7</t>
+          <t>14,11; 22,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,2; 35,58</t>
+          <t>24,67; 35,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,98; 31,56</t>
+          <t>22,1; 32,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 29,0</t>
+          <t>19,42; 28,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 17,82</t>
+          <t>11,58; 17,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,57; 34,49</t>
+          <t>26,65; 34,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,23; 33,48</t>
+          <t>25,95; 33,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,61; 29,47</t>
+          <t>22,45; 29,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,48; 18,91</t>
+          <t>13,68; 18,76</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 37,22</t>
+          <t>25,68; 37,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 39,72</t>
+          <t>28,56; 39,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 22,51</t>
+          <t>14,14; 22,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 26,37</t>
+          <t>14,56; 26,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,09; 37,87</t>
+          <t>26,81; 37,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 29,85</t>
+          <t>20,35; 29,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,79; 30,08</t>
+          <t>19,68; 28,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 37,91</t>
+          <t>15,18; 23,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,81; 35,56</t>
+          <t>28,03; 35,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,64; 32,9</t>
+          <t>25,52; 32,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 24,47</t>
+          <t>18,39; 24,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 31,61</t>
+          <t>16,17; 23,31</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,89; 35,62</t>
+          <t>21,68; 35,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,64; 38,8</t>
+          <t>24,68; 38,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,7; 32,23</t>
+          <t>17,31; 33,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 27,12</t>
+          <t>16,33; 26,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,99; 35,66</t>
+          <t>21,42; 35,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,51; 36,91</t>
+          <t>23,71; 37,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 31,39</t>
+          <t>17,52; 31,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 26,57</t>
+          <t>18,11; 25,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,64; 33,43</t>
+          <t>24,04; 33,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,98; 35,72</t>
+          <t>25,76; 36,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,69; 29,15</t>
+          <t>18,59; 29,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,16; 25,32</t>
+          <t>18,25; 24,42</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,03; 35,63</t>
+          <t>22,64; 35,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,41; 32,26</t>
+          <t>21,27; 32,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 28,35</t>
+          <t>17,25; 28,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,56; 28,03</t>
+          <t>18,56; 28,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,61; 32,47</t>
+          <t>20,23; 32,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,59; 32,43</t>
+          <t>21,25; 32,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,95; 26,94</t>
+          <t>16,73; 26,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,26</t>
+          <t>12,58; 19,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,06; 31,58</t>
+          <t>23,03; 31,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,89; 30,66</t>
+          <t>22,94; 30,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,27; 25,94</t>
+          <t>18,41; 25,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,8; 23,0</t>
+          <t>16,74; 23,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,9; 38,01</t>
+          <t>28,87; 37,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,22; 34,26</t>
+          <t>25,76; 33,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,01; 40,64</t>
+          <t>30,93; 40,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,26; 27,43</t>
+          <t>18,29; 26,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,83; 35,06</t>
+          <t>27,54; 35,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,82; 31,59</t>
+          <t>24,33; 31,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,78; 37,31</t>
+          <t>28,69; 37,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 21,72</t>
+          <t>18,33; 23,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,24; 34,97</t>
+          <t>29,31; 35,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,23; 31,65</t>
+          <t>26,06; 31,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,16; 37,5</t>
+          <t>31,28; 37,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 22,79</t>
+          <t>19,44; 24,01</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,78; 34,88</t>
+          <t>26,72; 34,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,26; 35,86</t>
+          <t>28,12; 36,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,01; 30,0</t>
+          <t>22,77; 29,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,31</t>
+          <t>7,96; 12,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,01; 39,15</t>
+          <t>31,19; 39,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,22; 37,26</t>
+          <t>29,99; 37,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,93; 30,74</t>
+          <t>23,89; 30,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,26; 14,13</t>
+          <t>10,24; 14,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,29; 35,98</t>
+          <t>30,3; 35,98</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,11; 35,43</t>
+          <t>30,25; 35,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,32; 29,16</t>
+          <t>24,16; 29,35</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 11,82</t>
+          <t>9,67; 12,74</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30,09; 33,87</t>
+          <t>30,02; 33,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,27; 31,98</t>
+          <t>28,35; 31,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25,99; 29,39</t>
+          <t>25,68; 29,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,8; 20,05</t>
+          <t>17,63; 20,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,36; 33,81</t>
+          <t>30,17; 33,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,43; 30,71</t>
+          <t>27,38; 30,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,69; 28,04</t>
+          <t>24,67; 27,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,53; 19,89</t>
+          <t>17,27; 19,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,82; 33,32</t>
+          <t>30,61; 33,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28,31; 30,67</t>
+          <t>28,23; 30,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25,61; 28,18</t>
+          <t>25,74; 28,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,51; 19,38</t>
+          <t>17,79; 19,76</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44237</t>
+          <t>51533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>64859</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>109096</t>
+          <t>126783</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55554; 81751</t>
+          <t>55572; 82255</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36195; 60288</t>
+          <t>35718; 61183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54706; 84334</t>
+          <t>53594; 84068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31714; 60131</t>
+          <t>39100; 65863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>68072; 98704</t>
+          <t>67300; 95644</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50662; 80638</t>
+          <t>51236; 81080</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42349; 68352</t>
+          <t>42347; 67923</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53776; 79821</t>
+          <t>61659; 88139</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>130891; 170114</t>
+          <t>132236; 171210</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92927; 133330</t>
+          <t>94161; 132120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103819; 142971</t>
+          <t>103222; 143145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90920; 132590</t>
+          <t>107525; 147178</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139687</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>109933</t>
+          <t>118313</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>249620</t>
+          <t>258433</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>119622; 158252</t>
+          <t>117758; 158410</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>105875; 143740</t>
+          <t>105795; 144320</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97406; 136071</t>
+          <t>99582; 137030</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113903; 170626</t>
+          <t>116306; 168603</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>118420; 155637</t>
+          <t>115232; 154994</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114994; 154533</t>
+          <t>116782; 156764</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87766; 122548</t>
+          <t>86694; 122581</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92759; 129753</t>
+          <t>101366; 137950</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>248806; 301791</t>
+          <t>248309; 305291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232809; 287378</t>
+          <t>231036; 285316</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>199472; 249932</t>
+          <t>198198; 251004</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>216151; 280441</t>
+          <t>226939; 290926</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54138</t>
+          <t>54556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47846</t>
+          <t>49416</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>101984</t>
+          <t>103972</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61048; 90528</t>
+          <t>60415; 89704</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80930; 111783</t>
+          <t>80478; 113780</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65398; 95764</t>
+          <t>66963; 96797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41162; 68359</t>
+          <t>42364; 68798</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72772; 102760</t>
+          <t>71234; 101535</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72275; 103740</t>
+          <t>72655; 105482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59465; 89247</t>
+          <t>59766; 89122</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38335; 59751</t>
+          <t>39563; 60451</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139574; 181191</t>
+          <t>139982; 182618</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163259; 208357</t>
+          <t>161498; 208732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135254; 176332</t>
+          <t>134295; 174241</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85812; 120365</t>
+          <t>87846; 120405</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59092</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>101370</t>
+          <t>79687</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>160463</t>
+          <t>151744</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69355; 99574</t>
+          <t>68699; 99657</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89428; 124350</t>
+          <t>89399; 123093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46973; 74295</t>
+          <t>46682; 74221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42432; 81789</t>
+          <t>53995; 97475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>81142; 113422</t>
+          <t>80310; 112573</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68726; 102337</t>
+          <t>69747; 102719</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69053; 104922</t>
+          <t>68656; 100839</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58776; 179504</t>
+          <t>63697; 100001</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>157700; 201655</t>
+          <t>158922; 202925</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>168171; 215794</t>
+          <t>167382; 216252</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123636; 166116</t>
+          <t>124883; 167293</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>117555; 247720</t>
+          <t>127767; 184244</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35951</t>
+          <t>39463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81812</t>
+          <t>87619</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37268; 60655</t>
+          <t>36916; 60669</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47319; 74513</t>
+          <t>47400; 74299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19910; 38426</t>
+          <t>20636; 39387</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28176; 45685</t>
+          <t>30904; 49971</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36495; 62007</t>
+          <t>37244; 61155</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45745; 71817</t>
+          <t>46127; 72994</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26230; 45679</t>
+          <t>25486; 45350</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38334; 53750</t>
+          <t>39801; 56786</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81380; 115050</t>
+          <t>82741; 113700</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100440; 138092</t>
+          <t>99598; 139510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49466; 77175</t>
+          <t>49220; 78911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71014; 93870</t>
+          <t>74652; 99899</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58662</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>40516</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98465</t>
+          <t>99158</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43580; 67433</t>
+          <t>42848; 66593</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51029; 80633</t>
+          <t>53160; 80102</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40169; 66223</t>
+          <t>40294; 66003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47102; 71132</t>
+          <t>46351; 71725</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42153; 66403</t>
+          <t>41370; 65586</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57177; 85881</t>
+          <t>56282; 86360</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41902; 66569</t>
+          <t>41335; 66453</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30883; 49913</t>
+          <t>31652; 50263</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>90788; 124358</t>
+          <t>90677; 125594</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>117848; 157843</t>
+          <t>118078; 159338</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87820; 124717</t>
+          <t>88512; 124766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>84036; 115025</t>
+          <t>83924; 115638</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139599</t>
+          <t>154097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>128721</t>
+          <t>154807</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>268320</t>
+          <t>308904</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>134196; 176500</t>
+          <t>134064; 176184</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>150075; 196057</t>
+          <t>147431; 192354</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>137167; 179736</t>
+          <t>136788; 181217</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>115528; 164467</t>
+          <t>127584; 182822</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>144729; 189091</t>
+          <t>148550; 191424</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>148913; 197500</t>
+          <t>152093; 198438</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>140158; 181739</t>
+          <t>139741; 180846</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>59144; 179755</t>
+          <t>135795; 175956</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>293446; 351038</t>
+          <t>294138; 356608</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>314096; 378964</t>
+          <t>312044; 378735</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>289606; 348521</t>
+          <t>290698; 351468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>165850; 325307</t>
+          <t>279653; 345418</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70323</t>
+          <t>78836</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>85772</t>
+          <t>97942</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>156095</t>
+          <t>176778</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>140750; 183317</t>
+          <t>140436; 183195</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>179170; 227334</t>
+          <t>178232; 229654</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>147318; 192066</t>
+          <t>145778; 191112</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31160; 102636</t>
+          <t>61249; 97840</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>183690; 231938</t>
+          <t>184792; 232473</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>212248; 261683</t>
+          <t>210651; 262531</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>165414; 212512</t>
+          <t>165129; 213215</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>72228; 99472</t>
+          <t>82936; 114576</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>338636; 402208</t>
+          <t>338719; 402275</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>402365; 473401</t>
+          <t>404246; 473040</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>323788; 388244</t>
+          <t>321657; 390772</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>96851; 190484</t>
+          <t>152791; 201384</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>649304</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>624166</t>
+          <t>664087</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1225855</t>
+          <t>1313391</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>738252; 831122</t>
+          <t>736551; 833872</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>823239; 931331</t>
+          <t>825376; 926135</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>692520; 783155</t>
+          <t>684125; 781855</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>462873; 672309</t>
+          <t>598651; 706277</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>832173; 926843</t>
+          <t>826844; 928824</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>862414; 965794</t>
+          <t>861046; 965161</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>707993; 804134</t>
+          <t>707403; 799371</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>520003; 711757</t>
+          <t>626031; 708473</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1600758; 1731109</t>
+          <t>1590088; 1727432</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1714290; 1857413</t>
+          <t>1709631; 1859926</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1416417; 1558872</t>
+          <t>1423747; 1555652</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1075093; 1342961</t>
+          <t>1248757; 1387336</t>
         </is>
       </c>
     </row>
